--- a/full-e2e-report.xlsx
+++ b/full-e2e-report.xlsx
@@ -43,7 +43,7 @@
     <t/>
   </si>
   <si>
-    <t>8/7/2026, 3:35:21 AM</t>
+    <t>8/7/2026, 3:55:25 AM</t>
   </si>
   <si>
     <t xml:space="preserve">TC002: Verify color contrast for readability in dark mode </t>

--- a/full-e2e-report.xlsx
+++ b/full-e2e-report.xlsx
@@ -43,7 +43,7 @@
     <t/>
   </si>
   <si>
-    <t>8/7/2026, 4:12:20 AM</t>
+    <t>8/7/2026, 5:03:51 AM</t>
   </si>
   <si>
     <t xml:space="preserve">TC002: Verify Redis cache stores active menu items </t>

--- a/full-e2e-report.xlsx
+++ b/full-e2e-report.xlsx
@@ -43,7 +43,7 @@
     <t/>
   </si>
   <si>
-    <t>8/7/2026, 5:03:51 AM</t>
+    <t>8/7/2026, 5:11:56 AM</t>
   </si>
   <si>
     <t xml:space="preserve">TC002: Verify Redis cache stores active menu items </t>

--- a/full-e2e-report.xlsx
+++ b/full-e2e-report.xlsx
@@ -43,7 +43,7 @@
     <t/>
   </si>
   <si>
-    <t>8/7/2026, 5:11:56 AM</t>
+    <t>8/7/2026, 5:18:18 AM</t>
   </si>
   <si>
     <t xml:space="preserve">TC002: Verify Redis cache stores active menu items </t>

--- a/full-e2e-report.xlsx
+++ b/full-e2e-report.xlsx
@@ -43,7 +43,7 @@
     <t/>
   </si>
   <si>
-    <t>8/7/2026, 5:18:18 AM</t>
+    <t>8/7/2026, 5:20:04 AM</t>
   </si>
   <si>
     <t xml:space="preserve">TC002: Verify Redis cache stores active menu items </t>

--- a/full-e2e-report.xlsx
+++ b/full-e2e-report.xlsx
@@ -43,7 +43,7 @@
     <t/>
   </si>
   <si>
-    <t>8/7/2026, 5:20:04 AM</t>
+    <t>8/7/2026, 5:31:58 AM</t>
   </si>
   <si>
     <t xml:space="preserve">TC002: Verify Redis cache stores active menu items </t>

--- a/full-e2e-report.xlsx
+++ b/full-e2e-report.xlsx
@@ -43,7 +43,7 @@
     <t/>
   </si>
   <si>
-    <t>8/7/2026, 5:31:58 AM</t>
+    <t>8/7/2026, 5:38:05 AM</t>
   </si>
   <si>
     <t xml:space="preserve">TC002: Verify Redis cache stores active menu items </t>

--- a/full-e2e-report.xlsx
+++ b/full-e2e-report.xlsx
@@ -43,7 +43,7 @@
     <t/>
   </si>
   <si>
-    <t>8/7/2026, 5:38:05 AM</t>
+    <t>8/7/2026, 5:45:10 AM</t>
   </si>
   <si>
     <t xml:space="preserve">TC002: Verify Redis cache stores active menu items </t>

--- a/full-e2e-report.xlsx
+++ b/full-e2e-report.xlsx
@@ -43,7 +43,7 @@
     <t/>
   </si>
   <si>
-    <t>8/7/2026, 5:45:10 AM</t>
+    <t>8/7/2026, 5:55:52 AM</t>
   </si>
   <si>
     <t xml:space="preserve">TC002: Verify Redis cache stores active menu items </t>

--- a/full-e2e-report.xlsx
+++ b/full-e2e-report.xlsx
@@ -43,7 +43,7 @@
     <t/>
   </si>
   <si>
-    <t>8/7/2026, 5:55:52 AM</t>
+    <t>8/7/2026, 6:14:45 AM</t>
   </si>
   <si>
     <t xml:space="preserve">TC002: Verify Redis cache stores active menu items </t>

--- a/full-e2e-report.xlsx
+++ b/full-e2e-report.xlsx
@@ -43,7 +43,7 @@
     <t/>
   </si>
   <si>
-    <t>8/7/2026, 6:14:45 AM</t>
+    <t>8/7/2026, 6:20:07 AM</t>
   </si>
   <si>
     <t xml:space="preserve">TC002: Verify Redis cache stores active menu items </t>

--- a/full-e2e-report.xlsx
+++ b/full-e2e-report.xlsx
@@ -43,7 +43,7 @@
     <t/>
   </si>
   <si>
-    <t>8/7/2026, 6:20:07 AM</t>
+    <t>8/7/2026, 6:30:06 AM</t>
   </si>
   <si>
     <t xml:space="preserve">TC002: Verify Redis cache stores active menu items </t>
